--- a/artfynd/A 55985-2024 artfynd.xlsx
+++ b/artfynd/A 55985-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,6 +1610,2898 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121659449</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500888</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7086084</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121659465</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>500617</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7086489</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121659462</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7086458</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121659464</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500589</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7086462</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121659471</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500582</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7086482</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121659468</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>501009</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7086218</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121659453</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>500629</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7086241</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121659457</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>500602</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7086312</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121659467</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>500843</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7086344</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121659470</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>500583</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7086344</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121659447</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500933</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7086021</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121659463</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>500577</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7086447</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121659469</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>501086</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7086250</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121659448</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>500901</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7086026</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121659451</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>500826</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7086192</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121659446</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>501031</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7086123</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121659459</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>500444</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7086336</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121659472</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>500654</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7086463</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121659452</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>500663</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7086244</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121659461</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>500441</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7086376</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121659458</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>500574</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7086322</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121659460</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>500439</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7086341</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121659445</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56201</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>500722</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7086246</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121659450</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>500768</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7086037</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121659454</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>500633</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7086253</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121659466</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>500839</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7086427</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121659455</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Risflokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>500632</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7086273</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55985-2024 artfynd.xlsx
+++ b/artfynd/A 55985-2024 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659449</v>
+        <v>121659461</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500888</v>
+        <v>500441</v>
       </c>
       <c r="R10" t="n">
-        <v>7086084</v>
+        <v>7086376</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659465</v>
+        <v>121659450</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500617</v>
+        <v>500768</v>
       </c>
       <c r="R11" t="n">
-        <v>7086489</v>
+        <v>7086037</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,7 +1830,7 @@
         <v>121659462</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121659464</v>
+        <v>121659458</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500589</v>
+        <v>500574</v>
       </c>
       <c r="R13" t="n">
-        <v>7086462</v>
+        <v>7086322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121659471</v>
+        <v>121659468</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500582</v>
+        <v>501009</v>
       </c>
       <c r="R14" t="n">
-        <v>7086482</v>
+        <v>7086218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121659468</v>
+        <v>121659470</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501009</v>
+        <v>500583</v>
       </c>
       <c r="R15" t="n">
-        <v>7086218</v>
+        <v>7086344</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121659453</v>
+        <v>121659457</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500629</v>
+        <v>500602</v>
       </c>
       <c r="R16" t="n">
-        <v>7086241</v>
+        <v>7086312</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121659457</v>
+        <v>121659451</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500602</v>
+        <v>500826</v>
       </c>
       <c r="R17" t="n">
-        <v>7086312</v>
+        <v>7086192</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121659467</v>
+        <v>121659453</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500843</v>
+        <v>500629</v>
       </c>
       <c r="R18" t="n">
-        <v>7086344</v>
+        <v>7086241</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121659470</v>
+        <v>121659449</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500583</v>
+        <v>500888</v>
       </c>
       <c r="R19" t="n">
-        <v>7086344</v>
+        <v>7086084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121659447</v>
+        <v>121659454</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500933</v>
+        <v>500633</v>
       </c>
       <c r="R20" t="n">
-        <v>7086021</v>
+        <v>7086253</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121659463</v>
+        <v>121659465</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500577</v>
+        <v>500617</v>
       </c>
       <c r="R21" t="n">
-        <v>7086447</v>
+        <v>7086489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121659469</v>
+        <v>121659459</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501086</v>
+        <v>500444</v>
       </c>
       <c r="R22" t="n">
-        <v>7086250</v>
+        <v>7086336</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121659448</v>
+        <v>121659472</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,21 +3020,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500901</v>
+        <v>500654</v>
       </c>
       <c r="R23" t="n">
-        <v>7086026</v>
+        <v>7086463</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121659451</v>
+        <v>121659445</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>56202</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,16 +3127,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100077</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3145,16 +3145,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500826</v>
+        <v>500722</v>
       </c>
       <c r="R24" t="n">
-        <v>7086192</v>
+        <v>7086246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3187,11 +3195,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,7 +3224,7 @@
         <v>121659446</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3325,10 +3328,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121659459</v>
+        <v>121659463</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,10 +3368,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500444</v>
+        <v>500577</v>
       </c>
       <c r="R26" t="n">
-        <v>7086336</v>
+        <v>7086447</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3432,10 +3435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121659472</v>
+        <v>121659447</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3448,21 +3451,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500654</v>
+        <v>500933</v>
       </c>
       <c r="R27" t="n">
-        <v>7086463</v>
+        <v>7086021</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3512,7 +3515,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3539,10 +3542,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121659452</v>
+        <v>121659466</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3579,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500663</v>
+        <v>500839</v>
       </c>
       <c r="R28" t="n">
-        <v>7086244</v>
+        <v>7086427</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3619,7 +3622,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3646,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121659461</v>
+        <v>121659452</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3686,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500441</v>
+        <v>500663</v>
       </c>
       <c r="R29" t="n">
-        <v>7086376</v>
+        <v>7086244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,10 +3756,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121659458</v>
+        <v>121659469</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,10 +3796,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500574</v>
+        <v>501086</v>
       </c>
       <c r="R30" t="n">
-        <v>7086322</v>
+        <v>7086250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3860,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121659460</v>
+        <v>121659455</v>
       </c>
       <c r="B31" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3900,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500439</v>
+        <v>500632</v>
       </c>
       <c r="R31" t="n">
-        <v>7086341</v>
+        <v>7086273</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3967,10 +3970,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121659445</v>
+        <v>121659460</v>
       </c>
       <c r="B32" t="n">
-        <v>56201</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3983,16 +3986,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100077</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4001,24 +4004,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500722</v>
+        <v>500439</v>
       </c>
       <c r="R32" t="n">
-        <v>7086246</v>
+        <v>7086341</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4051,6 +4046,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4077,10 +4077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121659450</v>
+        <v>121659471</v>
       </c>
       <c r="B33" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500768</v>
+        <v>500582</v>
       </c>
       <c r="R33" t="n">
-        <v>7086037</v>
+        <v>7086482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,10 +4184,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121659454</v>
+        <v>121659464</v>
       </c>
       <c r="B34" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500633</v>
+        <v>500589</v>
       </c>
       <c r="R34" t="n">
-        <v>7086253</v>
+        <v>7086462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121659466</v>
+        <v>121659467</v>
       </c>
       <c r="B35" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500839</v>
+        <v>500843</v>
       </c>
       <c r="R35" t="n">
-        <v>7086427</v>
+        <v>7086344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121659455</v>
+        <v>121659448</v>
       </c>
       <c r="B36" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500632</v>
+        <v>500901</v>
       </c>
       <c r="R36" t="n">
-        <v>7086273</v>
+        <v>7086026</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 55985-2024 artfynd.xlsx
+++ b/artfynd/A 55985-2024 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659465</v>
+        <v>121659462</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500617</v>
+        <v>500533</v>
       </c>
       <c r="R10" t="n">
-        <v>7086489</v>
+        <v>7086458</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659445</v>
+        <v>121659452</v>
       </c>
       <c r="B11" t="n">
-        <v>56202</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100077</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1754,24 +1754,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500722</v>
+        <v>500663</v>
       </c>
       <c r="R11" t="n">
-        <v>7086246</v>
+        <v>7086244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,6 +1796,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659451</v>
+        <v>121659460</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1870,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500826</v>
+        <v>500439</v>
       </c>
       <c r="R12" t="n">
-        <v>7086192</v>
+        <v>7086341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121659446</v>
+        <v>121659466</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1977,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501031</v>
+        <v>500839</v>
       </c>
       <c r="R13" t="n">
-        <v>7086123</v>
+        <v>7086427</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121659469</v>
+        <v>121659467</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2084,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501086</v>
+        <v>500843</v>
       </c>
       <c r="R14" t="n">
-        <v>7086250</v>
+        <v>7086344</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2148,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121659467</v>
+        <v>121659450</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2191,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500843</v>
+        <v>500768</v>
       </c>
       <c r="R15" t="n">
-        <v>7086344</v>
+        <v>7086037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121659455</v>
+        <v>121659448</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2298,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500632</v>
+        <v>500901</v>
       </c>
       <c r="R16" t="n">
-        <v>7086273</v>
+        <v>7086026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121659458</v>
+        <v>121659451</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2405,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500574</v>
+        <v>500826</v>
       </c>
       <c r="R17" t="n">
-        <v>7086322</v>
+        <v>7086192</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121659447</v>
+        <v>121659465</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2512,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500933</v>
+        <v>500617</v>
       </c>
       <c r="R18" t="n">
-        <v>7086021</v>
+        <v>7086489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2549,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121659452</v>
+        <v>121659454</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2619,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500663</v>
+        <v>500633</v>
       </c>
       <c r="R19" t="n">
-        <v>7086244</v>
+        <v>7086253</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2656,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121659449</v>
+        <v>121659464</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2726,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500888</v>
+        <v>500589</v>
       </c>
       <c r="R20" t="n">
-        <v>7086084</v>
+        <v>7086462</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121659448</v>
+        <v>121659461</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2833,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500901</v>
+        <v>500441</v>
       </c>
       <c r="R21" t="n">
-        <v>7086026</v>
+        <v>7086376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,7 +2897,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121659450</v>
+        <v>121659449</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2940,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500768</v>
+        <v>500888</v>
       </c>
       <c r="R22" t="n">
-        <v>7086037</v>
+        <v>7086084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,7 +3004,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121659462</v>
+        <v>121659455</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3047,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500533</v>
+        <v>500632</v>
       </c>
       <c r="R23" t="n">
-        <v>7086458</v>
+        <v>7086273</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3087,7 +3084,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3111,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121659457</v>
+        <v>121659458</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3154,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500602</v>
+        <v>500574</v>
       </c>
       <c r="R24" t="n">
-        <v>7086312</v>
+        <v>7086322</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3221,7 +3218,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121659463</v>
+        <v>121659468</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3261,10 +3258,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500577</v>
+        <v>501009</v>
       </c>
       <c r="R25" t="n">
-        <v>7086447</v>
+        <v>7086218</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,7 +3298,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,10 +3325,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121659470</v>
+        <v>121659469</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500583</v>
+        <v>501086</v>
       </c>
       <c r="R26" t="n">
-        <v>7086344</v>
+        <v>7086250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3408,7 +3405,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,7 +3432,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121659459</v>
+        <v>121659457</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3475,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500444</v>
+        <v>500602</v>
       </c>
       <c r="R27" t="n">
-        <v>7086336</v>
+        <v>7086312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3515,7 +3512,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,10 +3539,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121659466</v>
+        <v>121659470</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3558,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3582,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500839</v>
+        <v>500583</v>
       </c>
       <c r="R28" t="n">
-        <v>7086427</v>
+        <v>7086344</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3622,7 +3619,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,7 +3646,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121659453</v>
+        <v>121659447</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3689,10 +3686,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500629</v>
+        <v>500933</v>
       </c>
       <c r="R29" t="n">
-        <v>7086241</v>
+        <v>7086021</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3729,7 +3726,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,7 +3753,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121659464</v>
+        <v>121659459</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3796,10 +3793,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500589</v>
+        <v>500444</v>
       </c>
       <c r="R30" t="n">
-        <v>7086462</v>
+        <v>7086336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3863,7 +3860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121659468</v>
+        <v>121659453</v>
       </c>
       <c r="B31" t="n">
         <v>57357</v>
@@ -3903,10 +3900,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501009</v>
+        <v>500629</v>
       </c>
       <c r="R31" t="n">
-        <v>7086218</v>
+        <v>7086241</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3943,7 +3940,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,10 +3967,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121659454</v>
+        <v>121659471</v>
       </c>
       <c r="B32" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3986,21 +3983,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4007,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500633</v>
+        <v>500582</v>
       </c>
       <c r="R32" t="n">
-        <v>7086253</v>
+        <v>7086482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,7 +4047,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4077,10 +4074,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121659460</v>
+        <v>121659445</v>
       </c>
       <c r="B33" t="n">
-        <v>57357</v>
+        <v>56202</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4093,16 +4090,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100077</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4111,16 +4108,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500439</v>
+        <v>500722</v>
       </c>
       <c r="R33" t="n">
-        <v>7086341</v>
+        <v>7086246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4153,11 +4158,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,7 +4184,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121659461</v>
+        <v>121659446</v>
       </c>
       <c r="B34" t="n">
         <v>57357</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500441</v>
+        <v>501031</v>
       </c>
       <c r="R34" t="n">
-        <v>7086376</v>
+        <v>7086123</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121659471</v>
+        <v>121659463</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4414,21 +4414,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500582</v>
+        <v>500577</v>
       </c>
       <c r="R36" t="n">
-        <v>7086482</v>
+        <v>7086447</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 55985-2024 artfynd.xlsx
+++ b/artfynd/A 55985-2024 artfynd.xlsx
@@ -4074,10 +4074,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121659445</v>
+        <v>121659446</v>
       </c>
       <c r="B33" t="n">
-        <v>56202</v>
+        <v>57357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100077</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4108,24 +4108,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500722</v>
+        <v>501031</v>
       </c>
       <c r="R33" t="n">
-        <v>7086246</v>
+        <v>7086123</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,6 +4150,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,10 +4181,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121659446</v>
+        <v>121659445</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
+        <v>56202</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4200,16 +4197,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100077</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4218,16 +4215,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501031</v>
+        <v>500722</v>
       </c>
       <c r="R34" t="n">
-        <v>7086123</v>
+        <v>7086246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,11 +4265,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 55985-2024 artfynd.xlsx
+++ b/artfynd/A 55985-2024 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659462</v>
+        <v>121659465</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500533</v>
+        <v>500617</v>
       </c>
       <c r="R10" t="n">
-        <v>7086458</v>
+        <v>7086489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659452</v>
+        <v>121659467</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500663</v>
+        <v>500843</v>
       </c>
       <c r="R11" t="n">
-        <v>7086244</v>
+        <v>7086344</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659460</v>
+        <v>121659464</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500439</v>
+        <v>500589</v>
       </c>
       <c r="R12" t="n">
-        <v>7086341</v>
+        <v>7086462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121659466</v>
+        <v>121659462</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500839</v>
+        <v>500533</v>
       </c>
       <c r="R13" t="n">
-        <v>7086427</v>
+        <v>7086458</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121659467</v>
+        <v>121659463</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500843</v>
+        <v>500577</v>
       </c>
       <c r="R14" t="n">
-        <v>7086344</v>
+        <v>7086447</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121659450</v>
+        <v>121659445</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>56202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100077</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2182,16 +2182,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500768</v>
+        <v>500722</v>
       </c>
       <c r="R15" t="n">
-        <v>7086037</v>
+        <v>7086246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,11 +2232,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121659448</v>
+        <v>121659471</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500901</v>
+        <v>500582</v>
       </c>
       <c r="R16" t="n">
-        <v>7086026</v>
+        <v>7086482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2338,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121659451</v>
+        <v>121659446</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2402,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500826</v>
+        <v>501031</v>
       </c>
       <c r="R17" t="n">
-        <v>7086192</v>
+        <v>7086123</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2445,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,7 +2472,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121659465</v>
+        <v>121659460</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2509,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500617</v>
+        <v>500439</v>
       </c>
       <c r="R18" t="n">
-        <v>7086489</v>
+        <v>7086341</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121659454</v>
+        <v>121659468</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2616,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500633</v>
+        <v>501009</v>
       </c>
       <c r="R19" t="n">
-        <v>7086253</v>
+        <v>7086218</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2659,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,7 +2686,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121659464</v>
+        <v>121659469</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2723,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500589</v>
+        <v>501086</v>
       </c>
       <c r="R20" t="n">
-        <v>7086462</v>
+        <v>7086250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2766,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2793,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121659461</v>
+        <v>121659455</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2830,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500441</v>
+        <v>500632</v>
       </c>
       <c r="R21" t="n">
-        <v>7086376</v>
+        <v>7086273</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2873,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,7 +2900,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121659449</v>
+        <v>121659458</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2937,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500888</v>
+        <v>500574</v>
       </c>
       <c r="R22" t="n">
-        <v>7086084</v>
+        <v>7086322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3004,7 +3007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121659455</v>
+        <v>121659448</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3044,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500632</v>
+        <v>500901</v>
       </c>
       <c r="R23" t="n">
-        <v>7086273</v>
+        <v>7086026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,7 +3087,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,7 +3114,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121659458</v>
+        <v>121659451</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3151,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500574</v>
+        <v>500826</v>
       </c>
       <c r="R24" t="n">
-        <v>7086322</v>
+        <v>7086192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3218,7 +3221,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121659468</v>
+        <v>121659457</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3258,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501009</v>
+        <v>500602</v>
       </c>
       <c r="R25" t="n">
-        <v>7086218</v>
+        <v>7086312</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,7 +3328,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121659469</v>
+        <v>121659450</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3365,10 +3368,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501086</v>
+        <v>500768</v>
       </c>
       <c r="R26" t="n">
-        <v>7086250</v>
+        <v>7086037</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3432,7 +3435,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121659457</v>
+        <v>121659461</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3472,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500602</v>
+        <v>500441</v>
       </c>
       <c r="R27" t="n">
-        <v>7086312</v>
+        <v>7086376</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,10 +3542,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121659470</v>
+        <v>121659453</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3555,21 +3558,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500583</v>
+        <v>500629</v>
       </c>
       <c r="R28" t="n">
-        <v>7086344</v>
+        <v>7086241</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3619,7 +3622,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3646,7 +3649,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121659447</v>
+        <v>121659459</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3686,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500933</v>
+        <v>500444</v>
       </c>
       <c r="R29" t="n">
-        <v>7086021</v>
+        <v>7086336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3726,7 +3729,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,7 +3756,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121659459</v>
+        <v>121659454</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3793,10 +3796,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500444</v>
+        <v>500633</v>
       </c>
       <c r="R30" t="n">
-        <v>7086336</v>
+        <v>7086253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3860,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121659453</v>
+        <v>121659470</v>
       </c>
       <c r="B31" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3900,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500629</v>
+        <v>500583</v>
       </c>
       <c r="R31" t="n">
-        <v>7086241</v>
+        <v>7086344</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3943,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3967,7 +3970,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121659471</v>
+        <v>121659472</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -4007,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500582</v>
+        <v>500654</v>
       </c>
       <c r="R32" t="n">
-        <v>7086482</v>
+        <v>7086463</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4074,7 +4077,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121659446</v>
+        <v>121659449</v>
       </c>
       <c r="B33" t="n">
         <v>57357</v>
@@ -4114,10 +4117,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501031</v>
+        <v>500888</v>
       </c>
       <c r="R33" t="n">
-        <v>7086123</v>
+        <v>7086084</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,7 +4157,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4181,10 +4184,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121659445</v>
+        <v>121659466</v>
       </c>
       <c r="B34" t="n">
-        <v>56202</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4197,16 +4200,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100077</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4215,24 +4218,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Risflokojan, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500722</v>
+        <v>500839</v>
       </c>
       <c r="R34" t="n">
-        <v>7086246</v>
+        <v>7086427</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4265,6 +4260,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121659472</v>
+        <v>121659447</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500654</v>
+        <v>500933</v>
       </c>
       <c r="R35" t="n">
-        <v>7086463</v>
+        <v>7086021</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4398,7 +4398,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121659463</v>
+        <v>121659452</v>
       </c>
       <c r="B36" t="n">
         <v>57357</v>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500577</v>
+        <v>500663</v>
       </c>
       <c r="R36" t="n">
-        <v>7086447</v>
+        <v>7086244</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
